--- a/FYP/data/Simulation Data.xlsx
+++ b/FYP/data/Simulation Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/daicijun/Desktop/PolyU-LMS-FinalyearProject/FYP/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61C7DCEE-0DB5-AC46-92E8-ABA0C1C2A454}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43D5E0DE-BA05-464E-9322-0AE363A7F3FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="660" windowWidth="50880" windowHeight="26100" xr2:uid="{231FF3D6-D847-8C45-A418-0491AD0436BA}"/>
   </bookViews>
